--- a/data/trans_orig/IEDAD_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IEDAD_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39593</t>
+          <t>40591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32425</t>
+          <t>33450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48876</t>
+          <t>48362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67918</t>
+          <t>68449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24532</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>28962</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31640</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50486</t>
+          <t>50155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23505</t>
+          <t>24400</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38831</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31237</t>
+          <t>32042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45703</t>
+          <t>46334</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65541</t>
+          <t>66106</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20953</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31719</t>
+          <t>32009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113119</t>
+          <t>113219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>144432</t>
+          <t>143058</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>129582</t>
+          <t>130202</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>163930</t>
+          <t>162305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252193</t>
+          <t>250454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>295219</t>
+          <t>295322</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63798</t>
+          <t>63607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88941</t>
+          <t>89874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79794</t>
+          <t>79448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107651</t>
+          <t>106614</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152340</t>
+          <t>151101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188842</t>
+          <t>188334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133944</t>
+          <t>133921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166772</t>
+          <t>165749</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152406</t>
+          <t>152854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184819</t>
+          <t>185173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295572</t>
+          <t>296157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>341269</t>
+          <t>342017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73360</t>
+          <t>73895</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59546</t>
+          <t>59875</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84095</t>
+          <t>83746</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113949</t>
+          <t>114747</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148426</t>
+          <t>149283</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26517</t>
+          <t>26318</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44303</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26585</t>
+          <t>27189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43995</t>
+          <t>44003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57390</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82250</t>
+          <t>81348</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41849</t>
+          <t>41483</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19357</t>
+          <t>19372</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34471</t>
+          <t>33751</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>49218</t>
+          <t>48325</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>71217</t>
+          <t>71446</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60148</t>
+          <t>61823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82132</t>
+          <t>82595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51610</t>
+          <t>51607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71263</t>
+          <t>71204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118508</t>
+          <t>120091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147370</t>
+          <t>148557</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27584</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45185</t>
+          <t>46106</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28842</t>
+          <t>27935</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45176</t>
+          <t>44973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60260</t>
+          <t>59572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85005</t>
+          <t>83256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>176918</t>
+          <t>174392</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>215483</t>
+          <t>212913</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>186591</t>
+          <t>186670</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>225447</t>
+          <t>226659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>374105</t>
+          <t>373786</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>425977</t>
+          <t>426405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112564</t>
+          <t>112728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143706</t>
+          <t>145480</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126515</t>
+          <t>125461</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158968</t>
+          <t>158907</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>246623</t>
+          <t>243889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>293288</t>
+          <t>293918</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>231873</t>
+          <t>233216</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>272968</t>
+          <t>272686</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>234000</t>
+          <t>234279</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>274558</t>
+          <t>274336</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>478300</t>
+          <t>479200</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>535109</t>
+          <t>536949</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91204</t>
+          <t>91643</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121881</t>
+          <t>121584</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104755</t>
+          <t>105120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137348</t>
+          <t>136224</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207567</t>
+          <t>204209</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>250798</t>
+          <t>248646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23524</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38510</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20650</t>
+          <t>21053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35325</t>
+          <t>36031</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48244</t>
+          <t>48662</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70314</t>
+          <t>69673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>29755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11995</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31993</t>
+          <t>32186</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50368</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18004</t>
+          <t>18230</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32320</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18972</t>
+          <t>19407</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33628</t>
+          <t>33224</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40301</t>
+          <t>40431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61061</t>
+          <t>60810</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21480</t>
+          <t>20852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37887</t>
+          <t>38628</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91973</t>
+          <t>90995</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121305</t>
+          <t>120902</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105449</t>
+          <t>105501</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>135666</t>
+          <t>135681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>205384</t>
+          <t>203652</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>248010</t>
+          <t>245932</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>89660</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120062</t>
+          <t>118886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>95173</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126685</t>
+          <t>126775</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191092</t>
+          <t>193219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236381</t>
+          <t>237192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130305</t>
+          <t>131281</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164859</t>
+          <t>162588</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152767</t>
+          <t>154866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>189704</t>
+          <t>190988</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>296513</t>
+          <t>293724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>344860</t>
+          <t>342481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82318</t>
+          <t>82028</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111121</t>
+          <t>110703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78569</t>
+          <t>78214</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>108332</t>
+          <t>107412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>168172</t>
+          <t>168488</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>205617</t>
+          <t>210241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26525</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44945</t>
+          <t>45004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24870</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42558</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56573</t>
+          <t>56393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81369</t>
+          <t>80681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39693</t>
+          <t>39763</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22551</t>
+          <t>22499</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>39774</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>49559</t>
+          <t>49798</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>72277</t>
+          <t>72853</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54292</t>
+          <t>54180</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75832</t>
+          <t>75335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60744</t>
+          <t>60671</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82219</t>
+          <t>82134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120791</t>
+          <t>120767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>151574</t>
+          <t>150344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28288</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45648</t>
+          <t>46567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30372</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48636</t>
+          <t>48464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63620</t>
+          <t>63833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88741</t>
+          <t>88264</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>152255</t>
+          <t>154366</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>190566</t>
+          <t>190414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>161683</t>
+          <t>162331</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>202016</t>
+          <t>199342</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>322680</t>
+          <t>324987</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>378324</t>
+          <t>379339</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137787</t>
+          <t>138923</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175993</t>
+          <t>174947</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>139856</t>
+          <t>140929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>175628</t>
+          <t>178134</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>291067</t>
+          <t>289163</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>341686</t>
+          <t>342103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>215350</t>
+          <t>215093</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>255666</t>
+          <t>257090</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>247513</t>
+          <t>245239</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>290527</t>
+          <t>291037</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>475950</t>
+          <t>476054</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>535716</t>
+          <t>534483</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129366</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165299</t>
+          <t>166261</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129831</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>164773</t>
+          <t>164846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>267383</t>
+          <t>268016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>317105</t>
+          <t>317659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27965</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>45754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>22953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41510</t>
+          <t>41736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22948</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32678</t>
+          <t>32171</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33578</t>
+          <t>33196</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51299</t>
+          <t>51259</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>109748</t>
+          <t>111175</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>140952</t>
+          <t>141447</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102086</t>
+          <t>102123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133280</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>218583</t>
+          <t>219756</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>262572</t>
+          <t>268368</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115724</t>
+          <t>114654</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146830</t>
+          <t>145980</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114651</t>
+          <t>113959</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147676</t>
+          <t>146025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>237320</t>
+          <t>236675</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>280600</t>
+          <t>281741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122945</t>
+          <t>121835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154829</t>
+          <t>153742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149407</t>
+          <t>150397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184800</t>
+          <t>186461</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282994</t>
+          <t>282631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330037</t>
+          <t>327262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66800</t>
+          <t>67731</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93487</t>
+          <t>93750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63167</t>
+          <t>62346</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89432</t>
+          <t>89369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136678</t>
+          <t>135491</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>173055</t>
+          <t>173634</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41313</t>
+          <t>41325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28087</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46106</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56927</t>
+          <t>56127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80412</t>
+          <t>80996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33298</t>
+          <t>33381</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33381</t>
+          <t>33984</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>52643</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>71991</t>
+          <t>71784</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>100955</t>
+          <t>98997</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>46092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66207</t>
+          <t>65497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55438</t>
+          <t>56206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76784</t>
+          <t>76313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108204</t>
+          <t>106362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136936</t>
+          <t>135621</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33635</t>
+          <t>33951</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>52005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33139</t>
+          <t>33243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53158</t>
+          <t>52357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72717</t>
+          <t>72666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99369</t>
+          <t>99746</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>155049</t>
+          <t>156443</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>192500</t>
+          <t>193240</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>156425</t>
+          <t>154538</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193690</t>
+          <t>194595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>322658</t>
+          <t>320810</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>375614</t>
+          <t>377871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>171593</t>
+          <t>169578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210006</t>
+          <t>209164</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169707</t>
+          <t>168486</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>210307</t>
+          <t>209482</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>350807</t>
+          <t>350141</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>404421</t>
+          <t>407339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>192733</t>
+          <t>191420</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>231983</t>
+          <t>230469</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>238355</t>
+          <t>236554</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>279662</t>
+          <t>280704</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>438565</t>
+          <t>438129</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>497185</t>
+          <t>495088</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115609</t>
+          <t>116930</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>149111</t>
+          <t>149315</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108097</t>
+          <t>108183</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142287</t>
+          <t>140319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>233349</t>
+          <t>232145</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>278610</t>
+          <t>280910</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32618</t>
+          <t>32901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>30129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35832</t>
+          <t>33944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59529</t>
+          <t>57269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25291</t>
+          <t>26299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22816</t>
+          <t>23065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42287</t>
+          <t>43138</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19640</t>
+          <t>18908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>23625</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39903</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14822</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173159</t>
+          <t>173725</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>250565</t>
+          <t>244503</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>198935</t>
+          <t>197768</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>250076</t>
+          <t>246722</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>386241</t>
+          <t>386551</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>476918</t>
+          <t>473934</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92958</t>
+          <t>94968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134727</t>
+          <t>135697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114783</t>
+          <t>115189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154009</t>
+          <t>155376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222963</t>
+          <t>218377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279136</t>
+          <t>276917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82029</t>
+          <t>80842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121089</t>
+          <t>121082</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102594</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136766</t>
+          <t>137752</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>197241</t>
+          <t>198339</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250476</t>
+          <t>248823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31405</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52255</t>
+          <t>52841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>30528</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50796</t>
+          <t>50565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69245</t>
+          <t>68726</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>96505</t>
+          <t>96500</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43885</t>
+          <t>44681</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64218</t>
+          <t>63641</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49139</t>
+          <t>50016</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74122</t>
+          <t>73193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>101715</t>
+          <t>100203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132363</t>
+          <t>131252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>32928</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50055</t>
+          <t>50467</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>50722</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76768</t>
+          <t>76575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>89037</t>
+          <t>88416</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>121912</t>
+          <t>119982</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32414</t>
+          <t>32622</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50618</t>
+          <t>49411</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34323</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56390</t>
+          <t>55995</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71296</t>
+          <t>72530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>99548</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18731</t>
+          <t>18920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>21467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21184</t>
+          <t>21570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37507</t>
+          <t>36973</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>248524</t>
+          <t>247097</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>323800</t>
+          <t>325400</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>277715</t>
+          <t>276995</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>338660</t>
+          <t>336727</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>539742</t>
+          <t>542029</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>639114</t>
+          <t>639256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150819</t>
+          <t>144663</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196697</t>
+          <t>197012</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,82 +10089,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>29,64%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>212490</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>187258</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>237344</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>24,58%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>386378</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>351902</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>422199</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>27,08%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>24,67%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>29,59%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>188530</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>238720</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>386378</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>349050</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>423414</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>134118</t>
+          <t>136211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>178588</t>
+          <t>179096</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>162289</t>
+          <t>161554</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>204711</t>
+          <t>206013</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>307633</t>
+          <t>308323</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>370365</t>
+          <t>372165</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45864</t>
+          <t>46232</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>68795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49785</t>
+          <t>50215</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74241</t>
+          <t>74921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102468</t>
+          <t>101853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135881</t>
+          <t>135020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
